--- a/data/trans_dic/IP19C07-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C07-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por ortodoncia</t>
+          <t>Menores que en su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,79; 19,85</t>
+          <t>7,89; 20,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,0; 18,07</t>
+          <t>6,08; 19,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 15,26</t>
+          <t>4,01; 16,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 16,08</t>
+          <t>2,85; 15,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,84; 23,17</t>
+          <t>9,74; 24,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,9; 17,27</t>
+          <t>5,2; 17,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 13,83</t>
+          <t>3,11; 14,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,92</t>
+          <t>0,6; 6,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,23; 19,57</t>
+          <t>10,65; 19,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,73; 15,4</t>
+          <t>6,81; 15,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 12,22</t>
+          <t>4,53; 12,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 8,37</t>
+          <t>2,36; 8,78</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 12,77</t>
+          <t>4,54; 12,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 15,74</t>
+          <t>6,72; 15,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 16,61</t>
+          <t>5,77; 15,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 10,38</t>
+          <t>2,16; 10,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 14,67</t>
+          <t>5,33; 14,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 14,11</t>
+          <t>4,67; 12,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,65</t>
+          <t>1,19; 6,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 10,12</t>
+          <t>2,87; 10,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,12; 12,48</t>
+          <t>6,04; 11,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,62; 13,57</t>
+          <t>6,81; 13,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 9,57</t>
+          <t>4,02; 9,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 8,35</t>
+          <t>3,44; 8,58</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,35; 16,66</t>
+          <t>5,29; 16,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 15,35</t>
+          <t>3,98; 14,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,91</t>
+          <t>1,6; 9,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 16,11</t>
+          <t>5,29; 14,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 12,77</t>
+          <t>3,23; 12,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 14,82</t>
+          <t>4,72; 15,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 12,03</t>
+          <t>2,32; 11,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 14,22</t>
+          <t>4,35; 14,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 12,4</t>
+          <t>5,32; 12,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 12,68</t>
+          <t>5,58; 12,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 8,58</t>
+          <t>2,53; 8,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 12,38</t>
+          <t>5,77; 12,8</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,91; 25,75</t>
+          <t>11,74; 25,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 14,88</t>
+          <t>4,5; 14,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 15,16</t>
+          <t>4,97; 14,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,04; 15,46</t>
+          <t>4,85; 16,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 14,33</t>
+          <t>4,59; 14,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 18,29</t>
+          <t>7,34; 18,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 12,37</t>
+          <t>4,03; 13,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 11,46</t>
+          <t>2,91; 11,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,67; 18,22</t>
+          <t>9,06; 17,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 14,6</t>
+          <t>7,05; 14,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 11,88</t>
+          <t>5,61; 11,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 11,58</t>
+          <t>4,68; 11,07</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,37; 15,09</t>
+          <t>9,47; 15,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 12,55</t>
+          <t>7,26; 12,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,96; 11,05</t>
+          <t>5,88; 11,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,53</t>
+          <t>5,92; 10,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,67; 12,91</t>
+          <t>7,5; 12,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,56; 12,71</t>
+          <t>7,66; 12,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,05</t>
+          <t>4,04; 7,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,86</t>
+          <t>4,0; 8,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,16; 13,06</t>
+          <t>9,32; 13,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,1; 11,88</t>
+          <t>8,05; 11,8</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,55; 8,62</t>
+          <t>5,43; 8,6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,24</t>
+          <t>5,21; 8,17</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,51%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>10115</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8226</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5981</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12637</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7468</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1870</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>22751</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15694</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>11316</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>7143</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5971; 15879</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4542; 14181</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2838; 11883</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1991; 10783</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8005; 19797</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3915; 13241</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2355; 10853</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>515; 5418</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>16812; 30406</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>10205; 22758</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6648; 17936</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3655; 13617</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8839</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11924</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10685</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5981</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10345</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9795</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>9378</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>19184</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>21720</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>13986</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>15360</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4999; 13881</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7571; 17984</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6228; 16600</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2461; 11882</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5951; 15775</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5362; 14853</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1292; 7253</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4804; 16960</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>13392; 25770</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>15476; 29555</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>8700; 20455</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>9662; 24131</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6980</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6304</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10076</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5365</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7049</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4490</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>9747</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13353</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7578</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>19823</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3659; 11736</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2964; 10790</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1212; 7200</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5657; 15780</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2516; 9862</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3766; 12160</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1783; 8735</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5234; 16970</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>7831; 18783</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8610; 19238</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3858; 12808</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>13109; 29091</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>16964</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7884</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9938</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9028</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7881</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11841</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>6884</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>24845</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19724</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>17707</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>15913</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>11268; 24109</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4182; 13473</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5421; 16121</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4911; 16459</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>4129; 13400</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>7064; 18135</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4304; 13917</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3247; 12289</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>16851; 33254</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>13350; 27755</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>12101; 25545</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>9959; 23545</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>42898</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>34337</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>29692</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>30358</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36227</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>36153</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20895</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>27880</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>79125</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>70490</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>50587</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>58238</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>33248; 53716</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>25757; 43994</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>21373; 39972</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>23186; 41294</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>27139; 45993</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>28052; 47275</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>14857; 29276</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>19399; 38966</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>66442; 94353</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>58006; 85017</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>39744; 62906</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>45682; 71610</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C07-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C07-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,89; 20,98</t>
+          <t>7,71; 20,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,08; 19,0</t>
+          <t>5,82; 18,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 16,77</t>
+          <t>4,16; 15,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 15,46</t>
+          <t>3,04; 16,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,74; 24,09</t>
+          <t>9,16; 22,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,2; 17,6</t>
+          <t>5,52; 18,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 14,32</t>
+          <t>3,09; 14,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,36</t>
+          <t>0,59; 6,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,65; 19,26</t>
+          <t>10,4; 19,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,81; 15,18</t>
+          <t>6,79; 15,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 12,23</t>
+          <t>4,36; 12,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 8,78</t>
+          <t>2,17; 8,73</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 12,61</t>
+          <t>4,59; 13,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 15,97</t>
+          <t>6,6; 16,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 15,38</t>
+          <t>5,68; 16,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 10,45</t>
+          <t>2,29; 10,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 14,13</t>
+          <t>5,67; 14,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 12,95</t>
+          <t>4,81; 13,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,68</t>
+          <t>1,2; 6,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 10,13</t>
+          <t>3,06; 9,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,04; 11,62</t>
+          <t>5,94; 12,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,81; 13,0</t>
+          <t>6,53; 13,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,02; 9,45</t>
+          <t>3,94; 9,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 8,58</t>
+          <t>3,28; 8,5</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 16,96</t>
+          <t>5,34; 17,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 14,48</t>
+          <t>4,46; 14,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 9,53</t>
+          <t>1,54; 9,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 14,75</t>
+          <t>5,24; 15,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 12,66</t>
+          <t>3,38; 12,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,72; 15,25</t>
+          <t>4,62; 14,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 11,36</t>
+          <t>2,57; 11,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 14,11</t>
+          <t>4,18; 13,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,77</t>
+          <t>5,12; 13,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,58; 12,47</t>
+          <t>5,71; 12,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 8,4</t>
+          <t>2,7; 8,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 12,8</t>
+          <t>5,92; 12,49</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,74; 25,12</t>
+          <t>12,07; 24,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 14,49</t>
+          <t>4,62; 14,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 14,79</t>
+          <t>4,98; 15,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 16,27</t>
+          <t>4,59; 15,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 14,88</t>
+          <t>4,65; 15,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,34; 18,83</t>
+          <t>7,52; 18,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 13,04</t>
+          <t>3,86; 13,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 11,01</t>
+          <t>3,02; 11,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,06; 17,88</t>
+          <t>9,69; 17,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 14,66</t>
+          <t>7,04; 14,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,61; 11,84</t>
+          <t>5,2; 12,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 11,07</t>
+          <t>4,56; 11,21</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,47; 15,31</t>
+          <t>9,73; 15,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,26; 12,4</t>
+          <t>7,29; 12,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 11,0</t>
+          <t>5,93; 11,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,92; 10,54</t>
+          <t>5,64; 10,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,5; 12,71</t>
+          <t>7,79; 12,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,66; 12,92</t>
+          <t>7,58; 12,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,96</t>
+          <t>3,94; 7,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,04</t>
+          <t>4,12; 7,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,32; 13,24</t>
+          <t>9,35; 13,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,05; 11,8</t>
+          <t>8,09; 11,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,43; 8,6</t>
+          <t>5,57; 8,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,17</t>
+          <t>5,23; 8,22</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5971; 15879</t>
+          <t>5834; 15165</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4542; 14181</t>
+          <t>4347; 14032</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2838; 11883</t>
+          <t>2949; 11121</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1991; 10783</t>
+          <t>2120; 11206</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8005; 19797</t>
+          <t>7532; 18807</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3915; 13241</t>
+          <t>4155; 13753</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2355; 10853</t>
+          <t>2342; 11288</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>515; 5418</t>
+          <t>506; 5265</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16812; 30406</t>
+          <t>16423; 30151</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10205; 22758</t>
+          <t>10178; 23507</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6648; 17936</t>
+          <t>6398; 17837</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3655; 13617</t>
+          <t>3371; 13536</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4999; 13881</t>
+          <t>5050; 14506</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7571; 17984</t>
+          <t>7434; 18219</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6228; 16600</t>
+          <t>6131; 17727</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2461; 11882</t>
+          <t>2603; 11996</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5951; 15775</t>
+          <t>6331; 15837</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5362; 14853</t>
+          <t>5513; 15694</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1292; 7253</t>
+          <t>1300; 7307</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4804; 16960</t>
+          <t>5120; 16623</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13392; 25770</t>
+          <t>13171; 27339</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15476; 29555</t>
+          <t>14839; 29635</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8700; 20455</t>
+          <t>8526; 21089</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9662; 24131</t>
+          <t>9224; 23884</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3659; 11736</t>
+          <t>3696; 12121</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2964; 10790</t>
+          <t>3319; 10908</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1212; 7200</t>
+          <t>1165; 6962</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5657; 15780</t>
+          <t>5600; 16211</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2516; 9862</t>
+          <t>2634; 9852</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3766; 12160</t>
+          <t>3681; 11578</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1783; 8735</t>
+          <t>1973; 9122</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5234; 16970</t>
+          <t>5031; 15638</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7831; 18783</t>
+          <t>7524; 19173</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8610; 19238</t>
+          <t>8815; 19736</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3858; 12808</t>
+          <t>4118; 12581</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13109; 29091</t>
+          <t>13444; 28374</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11268; 24109</t>
+          <t>11582; 23929</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4182; 13473</t>
+          <t>4293; 13633</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5421; 16121</t>
+          <t>5432; 16468</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4911; 16459</t>
+          <t>4642; 15317</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4129; 13400</t>
+          <t>4183; 13700</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7064; 18135</t>
+          <t>7238; 18017</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4304; 13917</t>
+          <t>4118; 13953</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3247; 12289</t>
+          <t>3368; 12717</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16851; 33254</t>
+          <t>18025; 33286</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13350; 27755</t>
+          <t>13324; 28201</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12101; 25545</t>
+          <t>11226; 26655</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9959; 23545</t>
+          <t>9711; 23854</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33248; 53716</t>
+          <t>34135; 53121</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25757; 43994</t>
+          <t>25853; 43860</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21373; 39972</t>
+          <t>21548; 39995</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23186; 41294</t>
+          <t>22072; 41057</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27139; 45993</t>
+          <t>28173; 46308</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28052; 47275</t>
+          <t>27746; 46738</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14857; 29276</t>
+          <t>14488; 28954</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19399; 38966</t>
+          <t>19975; 38241</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>66442; 94353</t>
+          <t>66619; 94096</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58006; 85017</t>
+          <t>58317; 84678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39744; 62906</t>
+          <t>40738; 63133</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>45682; 71610</t>
+          <t>45816; 72029</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C07-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C07-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15,38%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>13,37%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11,02%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8,44%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7,56%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,38%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>14,41%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,71; 20,04</t>
+          <t>9,84; 23,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 18,8</t>
+          <t>4,9; 17,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 15,7</t>
+          <t>3,08; 13,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 16,06</t>
+          <t>0,64; 6,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,16; 22,88</t>
+          <t>7,79; 19,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,52; 18,28</t>
+          <t>6,0; 18,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 14,89</t>
+          <t>3,76; 15,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,18</t>
+          <t>3,18; 16,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,4; 19,1</t>
+          <t>10,23; 19,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,79; 15,68</t>
+          <t>6,73; 15,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 12,16</t>
+          <t>4,42; 12,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,73</t>
+          <t>2,43; 8,92</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,54%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>8,03%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>10,59%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>9,9%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,54%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 13,18</t>
+          <t>5,74; 14,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 16,18</t>
+          <t>4,89; 14,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,68; 16,42</t>
+          <t>1,19; 6,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 10,55</t>
+          <t>3,08; 10,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,67; 14,19</t>
+          <t>4,61; 12,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 13,68</t>
+          <t>6,85; 15,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,73</t>
+          <t>6,11; 16,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 9,93</t>
+          <t>2,3; 10,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,94; 12,33</t>
+          <t>6,12; 12,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,53; 13,04</t>
+          <t>6,62; 13,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 9,74</t>
+          <t>4,13; 9,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 8,5</t>
+          <t>3,35; 8,63</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,84%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>10,09%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>8,46%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4,09%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 17,51</t>
+          <t>3,26; 12,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 14,64</t>
+          <t>4,93; 14,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 9,21</t>
+          <t>2,63; 12,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 15,16</t>
+          <t>4,37; 15,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 12,65</t>
+          <t>5,35; 16,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 14,52</t>
+          <t>4,33; 15,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 11,87</t>
+          <t>1,57; 8,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 13,01</t>
+          <t>5,47; 16,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 13,04</t>
+          <t>5,19; 12,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 12,79</t>
+          <t>5,63; 12,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,25</t>
+          <t>2,71; 8,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,92; 12,49</t>
+          <t>6,31; 13,31</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12,3%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,58%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>17,67%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8,48%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9,12%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,07; 24,93</t>
+          <t>4,43; 14,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 14,66</t>
+          <t>7,24; 18,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 15,11</t>
+          <t>3,82; 12,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 15,14</t>
+          <t>3,11; 12,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 15,21</t>
+          <t>11,91; 25,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 18,71</t>
+          <t>4,52; 14,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 13,07</t>
+          <t>5,08; 15,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 11,4</t>
+          <t>5,04; 15,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,69; 17,89</t>
+          <t>9,67; 18,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 14,9</t>
+          <t>6,92; 14,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 12,35</t>
+          <t>5,24; 11,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 11,21</t>
+          <t>4,96; 11,83</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>12,22%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>9,68%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>8,17%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,73; 15,14</t>
+          <t>7,67; 12,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 12,36</t>
+          <t>7,56; 12,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,93; 11,01</t>
+          <t>4,08; 8,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,64; 10,48</t>
+          <t>4,29; 8,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 12,8</t>
+          <t>9,37; 15,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,58; 12,77</t>
+          <t>7,43; 12,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,87</t>
+          <t>5,96; 11,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,89</t>
+          <t>5,77; 10,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,35; 13,2</t>
+          <t>9,16; 13,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,09; 11,75</t>
+          <t>8,1; 11,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 8,63</t>
+          <t>5,55; 8,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,22</t>
+          <t>5,31; 8,52</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12637</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7468</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>10115</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>8226</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>5981</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5272</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>12637</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7468</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5335</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>7432</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5834; 15165</t>
+          <t>8084; 19043</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4347; 14032</t>
+          <t>3688; 12997</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2949; 11121</t>
+          <t>2335; 10485</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2120; 11206</t>
+          <t>524; 5040</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7532; 18807</t>
+          <t>5896; 15020</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4155; 13753</t>
+          <t>4481; 13489</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2342; 11288</t>
+          <t>2665; 10809</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>506; 5265</t>
+          <t>2359; 12123</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16423; 30151</t>
+          <t>16144; 30896</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10178; 23507</t>
+          <t>10090; 23091</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6398; 17837</t>
+          <t>6480; 17919</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3371; 13536</t>
+          <t>3783; 13898</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10345</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9795</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9444</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8839</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11924</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10685</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5981</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10345</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9795</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3301</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15360</t>
+          <t>15800</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5050; 14506</t>
+          <t>6411; 16382</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7434; 18219</t>
+          <t>5614; 16186</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6131; 17727</t>
+          <t>1289; 7226</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2603; 11996</t>
+          <t>4994; 17315</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6331; 15837</t>
+          <t>5069; 14054</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5513; 15694</t>
+          <t>7713; 17718</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1300; 7307</t>
+          <t>6592; 17938</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5120; 16623</t>
+          <t>2685; 12849</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13171; 27339</t>
+          <t>13578; 27659</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14839; 29635</t>
+          <t>15045; 30837</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8526; 21089</t>
+          <t>8945; 20727</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9224; 23884</t>
+          <t>9352; 24107</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5365</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7049</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4490</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9735</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>6980</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>6304</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3088</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10076</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5365</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7049</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4490</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9747</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19823</t>
+          <t>20055</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3696; 12121</t>
+          <t>2537; 9947</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3319; 10908</t>
+          <t>3936; 11822</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1165; 6962</t>
+          <t>2020; 9249</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5600; 16211</t>
+          <t>4899; 16879</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2634; 9852</t>
+          <t>3703; 11528</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3681; 11578</t>
+          <t>3228; 11434</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1973; 9122</t>
+          <t>1184; 6734</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5031; 15638</t>
+          <t>5606; 17274</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7524; 19173</t>
+          <t>7634; 18233</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8815; 19736</t>
+          <t>8680; 19561</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4118; 12581</t>
+          <t>4131; 13073</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13444; 28374</t>
+          <t>13537; 28558</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7881</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11841</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6921</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>16964</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>7884</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>9938</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9028</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7881</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11841</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>9174</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15913</t>
+          <t>16095</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11582; 23929</t>
+          <t>3992; 12904</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4293; 13633</t>
+          <t>6975; 17614</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5432; 16468</t>
+          <t>4074; 13208</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4642; 15317</t>
+          <t>3267; 12912</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4183; 13700</t>
+          <t>11430; 24714</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7238; 18017</t>
+          <t>4203; 13837</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4118; 13953</t>
+          <t>5539; 16523</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3368; 12717</t>
+          <t>5170; 15808</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18025; 33286</t>
+          <t>17986; 33887</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13324; 28201</t>
+          <t>13092; 27643</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11226; 26655</t>
+          <t>11299; 25634</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9711; 23854</t>
+          <t>10310; 24571</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>36227</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>36153</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20895</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>27914</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>42898</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>34337</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>29692</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>30358</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>36227</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>36153</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>20895</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27880</t>
+          <t>31469</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>58238</t>
+          <t>59383</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>34135; 53121</t>
+          <t>27746; 46699</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25853; 43860</t>
+          <t>27652; 46512</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21548; 39995</t>
+          <t>15014; 29636</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22072; 41057</t>
+          <t>19800; 38307</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28173; 46308</t>
+          <t>32872; 52969</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27746; 46738</t>
+          <t>26370; 44516</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14488; 28954</t>
+          <t>21653; 40170</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19975; 38241</t>
+          <t>22847; 42910</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>66619; 94096</t>
+          <t>65315; 93057</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58317; 84678</t>
+          <t>58351; 85608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40738; 63133</t>
+          <t>40567; 63057</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>45816; 72029</t>
+          <t>45499; 73060</t>
         </is>
       </c>
     </row>
